--- a/artfynd/A 37723-2025 artfynd.xlsx
+++ b/artfynd/A 37723-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153181</v>
       </c>
       <c r="B2" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137153191</v>
       </c>
       <c r="B3" t="n">
-        <v>92701</v>
+        <v>92703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>137153192</v>
       </c>
       <c r="B4" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137153182</v>
       </c>
       <c r="B5" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137153183</v>
       </c>
       <c r="B6" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>137153184</v>
       </c>
       <c r="B7" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>137153185</v>
       </c>
       <c r="B8" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>137153186</v>
       </c>
       <c r="B9" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>137153194</v>
       </c>
       <c r="B10" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>137153190</v>
       </c>
       <c r="B11" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>137153187</v>
       </c>
       <c r="B12" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37723-2025 artfynd.xlsx
+++ b/artfynd/A 37723-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153181</v>
       </c>
       <c r="B2" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137153191</v>
       </c>
       <c r="B3" t="n">
-        <v>92703</v>
+        <v>92716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>137153192</v>
       </c>
       <c r="B4" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137153182</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137153183</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>137153184</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>137153185</v>
       </c>
       <c r="B8" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>137153186</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>137153194</v>
       </c>
       <c r="B10" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>137153190</v>
       </c>
       <c r="B11" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>137153187</v>
       </c>
       <c r="B12" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37723-2025 artfynd.xlsx
+++ b/artfynd/A 37723-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153181</v>
       </c>
       <c r="B2" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137153191</v>
       </c>
       <c r="B3" t="n">
-        <v>92716</v>
+        <v>92718</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>137153192</v>
       </c>
       <c r="B4" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137153182</v>
       </c>
       <c r="B5" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137153183</v>
       </c>
       <c r="B6" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>137153184</v>
       </c>
       <c r="B7" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>137153185</v>
       </c>
       <c r="B8" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>137153186</v>
       </c>
       <c r="B9" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>137153194</v>
       </c>
       <c r="B10" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>137153190</v>
       </c>
       <c r="B11" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>137153187</v>
       </c>
       <c r="B12" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37723-2025 artfynd.xlsx
+++ b/artfynd/A 37723-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>137153191</v>
       </c>
       <c r="B3" t="n">
-        <v>92718</v>
+        <v>92721</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>137153192</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37723-2025 artfynd.xlsx
+++ b/artfynd/A 37723-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153181</v>
       </c>
       <c r="B2" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137153191</v>
       </c>
       <c r="B3" t="n">
-        <v>92721</v>
+        <v>92731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>137153192</v>
       </c>
       <c r="B4" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137153182</v>
       </c>
       <c r="B5" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137153183</v>
       </c>
       <c r="B6" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>137153184</v>
       </c>
       <c r="B7" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>137153185</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>137153186</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>137153194</v>
       </c>
       <c r="B10" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>137153190</v>
       </c>
       <c r="B11" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>137153187</v>
       </c>
       <c r="B12" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37723-2025 artfynd.xlsx
+++ b/artfynd/A 37723-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>137153191</v>
       </c>
       <c r="B3" t="n">
-        <v>92731</v>
+        <v>92732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>137153192</v>
       </c>
       <c r="B4" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37723-2025 artfynd.xlsx
+++ b/artfynd/A 37723-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153181</v>
       </c>
       <c r="B2" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137153191</v>
       </c>
       <c r="B3" t="n">
-        <v>92732</v>
+        <v>92735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>137153192</v>
       </c>
       <c r="B4" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137153182</v>
       </c>
       <c r="B5" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137153183</v>
       </c>
       <c r="B6" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>137153184</v>
       </c>
       <c r="B7" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>137153185</v>
       </c>
       <c r="B8" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>137153186</v>
       </c>
       <c r="B9" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>137153194</v>
       </c>
       <c r="B10" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>137153190</v>
       </c>
       <c r="B11" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>137153187</v>
       </c>
       <c r="B12" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37723-2025 artfynd.xlsx
+++ b/artfynd/A 37723-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>137153191</v>
       </c>
       <c r="B3" t="n">
-        <v>92735</v>
+        <v>92737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>137153192</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37723-2025 artfynd.xlsx
+++ b/artfynd/A 37723-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153181</v>
       </c>
       <c r="B2" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137153191</v>
       </c>
       <c r="B3" t="n">
-        <v>92737</v>
+        <v>92742</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>137153192</v>
       </c>
       <c r="B4" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137153182</v>
       </c>
       <c r="B5" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137153183</v>
       </c>
       <c r="B6" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>137153184</v>
       </c>
       <c r="B7" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>137153185</v>
       </c>
       <c r="B8" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>137153186</v>
       </c>
       <c r="B9" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>137153194</v>
       </c>
       <c r="B10" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>137153190</v>
       </c>
       <c r="B11" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>137153187</v>
       </c>
       <c r="B12" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37723-2025 artfynd.xlsx
+++ b/artfynd/A 37723-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153181</v>
       </c>
       <c r="B2" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137153191</v>
       </c>
       <c r="B3" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>137153192</v>
       </c>
       <c r="B4" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137153182</v>
       </c>
       <c r="B5" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137153183</v>
       </c>
       <c r="B6" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>137153184</v>
       </c>
       <c r="B7" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>137153185</v>
       </c>
       <c r="B8" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>137153186</v>
       </c>
       <c r="B9" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>137153194</v>
       </c>
       <c r="B10" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>137153190</v>
       </c>
       <c r="B11" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>137153187</v>
       </c>
       <c r="B12" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37723-2025 artfynd.xlsx
+++ b/artfynd/A 37723-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153181</v>
       </c>
       <c r="B2" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137153191</v>
       </c>
       <c r="B3" t="n">
-        <v>92754</v>
+        <v>92755</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>137153192</v>
       </c>
       <c r="B4" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137153182</v>
       </c>
       <c r="B5" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137153183</v>
       </c>
       <c r="B6" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>137153184</v>
       </c>
       <c r="B7" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>137153185</v>
       </c>
       <c r="B8" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>137153186</v>
       </c>
       <c r="B9" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>137153194</v>
       </c>
       <c r="B10" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>137153190</v>
       </c>
       <c r="B11" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>137153187</v>
       </c>
       <c r="B12" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37723-2025 artfynd.xlsx
+++ b/artfynd/A 37723-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153181</v>
       </c>
       <c r="B2" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137153191</v>
       </c>
       <c r="B3" t="n">
-        <v>92755</v>
+        <v>92758</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>137153192</v>
       </c>
       <c r="B4" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137153182</v>
       </c>
       <c r="B5" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137153183</v>
       </c>
       <c r="B6" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>137153184</v>
       </c>
       <c r="B7" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>137153185</v>
       </c>
       <c r="B8" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>137153186</v>
       </c>
       <c r="B9" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>137153194</v>
       </c>
       <c r="B10" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>137153190</v>
       </c>
       <c r="B11" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>137153187</v>
       </c>
       <c r="B12" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37723-2025 artfynd.xlsx
+++ b/artfynd/A 37723-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153181</v>
       </c>
       <c r="B2" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137153191</v>
       </c>
       <c r="B3" t="n">
-        <v>92758</v>
+        <v>92762</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>137153192</v>
       </c>
       <c r="B4" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137153182</v>
       </c>
       <c r="B5" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137153183</v>
       </c>
       <c r="B6" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>137153184</v>
       </c>
       <c r="B7" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>137153185</v>
       </c>
       <c r="B8" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>137153186</v>
       </c>
       <c r="B9" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>137153194</v>
       </c>
       <c r="B10" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>137153190</v>
       </c>
       <c r="B11" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>137153187</v>
       </c>
       <c r="B12" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
